--- a/public/file/Trax Book Retail Shipment Template New.xlsx
+++ b/public/file/Trax Book Retail Shipment Template New.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\sonic\public\file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C68DD48D-50AF-4054-8856-95946EF43B5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{608DD421-8257-44F1-9A2A-36E8E5B0BD50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/public/file/Trax Book Retail Shipment Template New.xlsx
+++ b/public/file/Trax Book Retail Shipment Template New.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\sonic\public\file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{608DD421-8257-44F1-9A2A-36E8E5B0BD50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7E976B6-13D8-41F2-881C-5FC64BCC7D79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -120,10 +120,10 @@
     <t>Admin Discount</t>
   </si>
   <si>
-    <t>Parcel Amount</t>
-  </si>
-  <si>
     <t>Quantity</t>
+  </si>
+  <si>
+    <t>Parcel Value</t>
   </si>
 </sst>
 </file>
@@ -616,10 +616,10 @@
         <v>29</v>
       </c>
       <c r="AF1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AG1" s="1" t="s">
         <v>31</v>
-      </c>
-      <c r="AG1" s="1" t="s">
-        <v>32</v>
       </c>
     </row>
   </sheetData>
